--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1482,7 +1482,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4747" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4749" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -617,7 +617,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -642,7 +645,10 @@
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -901,10 +907,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -3992,22 +3998,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>186</v>
@@ -4034,10 +4042,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -4045,13 +4053,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -4061,7 +4069,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -4076,13 +4084,13 @@
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>191</v>
@@ -4114,7 +4122,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4156,10 +4164,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4167,10 +4175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4193,13 +4201,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4250,7 +4258,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4274,7 +4282,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4285,10 +4293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4317,7 +4325,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4358,19 +4366,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4394,7 +4402,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4405,10 +4413,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4431,19 +4439,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4492,7 +4500,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4513,10 +4521,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4527,10 +4535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4553,13 +4561,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4610,7 +4618,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4634,7 +4642,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4645,10 +4653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4677,7 +4685,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4718,19 +4726,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4754,7 +4762,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4765,10 +4773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4794,23 +4802,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4852,7 +4860,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4873,10 +4881,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4887,10 +4895,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4913,16 +4921,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4972,7 +4980,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4993,10 +5001,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5007,10 +5015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5036,21 +5044,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5092,7 +5100,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5113,10 +5121,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5127,10 +5135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5153,17 +5161,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5173,7 +5181,7 @@
         <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>83</v>
@@ -5212,7 +5220,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5233,10 +5241,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5247,10 +5255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5273,19 +5281,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5334,7 +5342,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5355,10 +5363,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5369,10 +5377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5395,19 +5403,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5456,7 +5464,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5477,10 +5485,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5491,13 +5499,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5522,13 +5530,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>191</v>
@@ -5556,11 +5564,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>286</v>
+        <v>193</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5602,10 +5612,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5613,10 +5623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5639,13 +5649,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5696,7 +5706,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5720,7 +5730,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5731,10 +5741,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5763,7 +5773,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5804,19 +5814,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5840,7 +5850,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5851,10 +5861,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5877,19 +5887,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5938,7 +5948,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5959,10 +5969,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5973,10 +5983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5999,13 +6009,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6056,7 +6066,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6080,7 +6090,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6091,10 +6101,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6123,7 +6133,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6164,19 +6174,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6200,7 +6210,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6211,10 +6221,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6240,23 +6250,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6298,7 +6308,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6319,10 +6329,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6333,10 +6343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6359,16 +6369,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6418,7 +6428,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6439,10 +6449,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6453,10 +6463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6482,21 +6492,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6538,7 +6548,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6559,10 +6569,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6573,10 +6583,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6599,17 +6609,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6658,7 +6668,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6679,10 +6689,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6693,10 +6703,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6719,19 +6729,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6780,7 +6790,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6801,10 +6811,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6815,10 +6825,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6841,19 +6851,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6902,7 +6912,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6923,10 +6933,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6937,13 +6947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6968,13 +6978,13 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>191</v>
@@ -7006,7 +7016,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7048,10 +7058,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7059,10 +7069,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7085,13 +7095,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7142,7 +7152,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7166,7 +7176,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7177,10 +7187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7209,7 +7219,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7250,19 +7260,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7286,7 +7296,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7297,10 +7307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7323,19 +7333,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7384,7 +7394,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7405,10 +7415,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7419,10 +7429,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7445,13 +7455,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7502,7 +7512,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7526,7 +7536,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7537,10 +7547,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7569,7 +7579,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7610,19 +7620,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7646,7 +7656,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7657,10 +7667,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7686,23 +7696,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7744,7 +7754,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7765,10 +7775,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7779,10 +7789,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7805,16 +7815,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7864,7 +7874,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7885,10 +7895,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7899,10 +7909,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7928,21 +7938,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7984,7 +7994,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8005,10 +8015,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8019,10 +8029,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8045,17 +8055,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8104,7 +8114,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8125,10 +8135,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8139,10 +8149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8165,19 +8175,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8226,7 +8236,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8247,10 +8257,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8261,10 +8271,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8287,19 +8297,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8348,7 +8358,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8369,10 +8379,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8383,14 +8393,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8412,16 +8422,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8446,13 +8456,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8470,7 +8480,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8485,30 +8495,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8531,13 +8541,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8588,7 +8598,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8612,7 +8622,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8623,10 +8633,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8655,7 +8665,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8696,19 +8706,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8732,7 +8742,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8743,10 +8753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8769,19 +8779,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8830,7 +8840,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8851,10 +8861,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8865,10 +8875,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8891,13 +8901,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8948,7 +8958,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8972,7 +8982,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8983,10 +8993,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9015,7 +9025,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9056,19 +9066,19 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9092,7 +9102,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9103,10 +9113,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9132,23 +9142,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9190,7 +9200,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9211,10 +9221,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9225,10 +9235,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9251,16 +9261,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9310,7 +9320,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9331,10 +9341,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9345,10 +9355,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9374,21 +9384,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9430,7 +9440,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9451,10 +9461,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9465,10 +9475,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9491,17 +9501,17 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9511,7 +9521,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9550,7 +9560,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9571,10 +9581,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9585,10 +9595,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9611,19 +9621,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9672,7 +9682,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9693,10 +9703,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9707,10 +9717,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9733,19 +9743,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9794,7 +9804,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9815,10 +9825,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9829,10 +9839,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9855,19 +9865,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9916,7 +9926,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9931,19 +9941,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9951,10 +9961,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9977,7 +9987,7 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>162</v>
@@ -9986,7 +9996,7 @@
         <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10036,7 +10046,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10057,13 +10067,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10071,14 +10081,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10097,19 +10107,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10158,7 +10168,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10173,19 +10183,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10193,14 +10203,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10219,19 +10229,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10280,7 +10290,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10295,19 +10305,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10315,10 +10325,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10341,16 +10351,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10400,7 +10410,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10421,13 +10431,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10435,10 +10445,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10461,19 +10471,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10522,7 +10532,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10537,19 +10547,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10557,10 +10567,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10586,16 +10596,16 @@
         <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10644,7 +10654,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10653,7 +10663,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10662,27 +10672,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10708,16 +10718,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10742,13 +10752,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10766,7 +10776,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10775,7 +10785,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10790,7 +10800,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10801,14 +10811,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10836,10 +10846,10 @@
         <v>162</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10864,13 +10874,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10888,7 +10898,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10906,27 +10916,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10949,7 +10959,7 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>162</v>
@@ -10958,10 +10968,10 @@
         <v>162</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11010,7 +11020,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11031,10 +11041,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11045,10 +11055,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11074,13 +11084,13 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11110,7 +11120,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11128,7 +11138,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11146,27 +11156,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11189,13 +11199,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11246,7 +11256,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11270,7 +11280,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11281,10 +11291,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11313,7 +11323,7 @@
         <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11354,19 +11364,19 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11390,7 +11400,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11401,13 +11411,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11429,13 +11439,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11486,7 +11496,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11521,10 +11531,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11547,19 +11557,19 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11608,7 +11618,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11629,10 +11639,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11643,10 +11653,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11669,19 +11679,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11730,7 +11740,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11751,10 +11761,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11765,10 +11775,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11794,16 +11804,16 @@
         <v>188</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -11828,13 +11838,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -11852,7 +11862,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11873,10 +11883,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11887,10 +11897,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11913,7 +11923,7 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>162</v>
@@ -11922,7 +11932,7 @@
         <v>162</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11972,7 +11982,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11990,27 +12000,27 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12033,16 +12043,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12092,7 +12102,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12110,27 +12120,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12153,7 +12163,7 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>162</v>
@@ -12162,10 +12172,10 @@
         <v>162</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12214,7 +12224,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12226,7 +12236,7 @@
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12235,10 +12245,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12249,10 +12259,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12275,13 +12285,13 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12332,7 +12342,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12356,7 +12366,7 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12367,10 +12377,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12399,7 +12409,7 @@
         <v>141</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>143</v>
@@ -12452,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12476,7 +12486,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12487,14 +12497,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12516,10 +12526,10 @@
         <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -12574,7 +12584,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12609,10 +12619,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12635,13 +12645,13 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12692,7 +12702,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12701,7 +12711,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -12713,10 +12723,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12727,10 +12737,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12753,13 +12763,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12810,7 +12820,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12819,7 +12829,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12831,10 +12841,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12845,10 +12855,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12874,16 +12884,16 @@
         <v>188</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12911,10 +12921,10 @@
         <v>118</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -12932,7 +12942,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12950,13 +12960,13 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12967,10 +12977,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12996,16 +13006,16 @@
         <v>188</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13030,13 +13040,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13054,7 +13064,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13072,13 +13082,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13089,10 +13099,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13115,17 +13125,17 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13174,7 +13184,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13198,7 +13208,7 @@
         <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13209,10 +13219,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13235,13 +13245,13 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13292,7 +13302,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13313,10 +13323,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13327,10 +13337,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13353,16 +13363,16 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13412,7 +13422,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13433,10 +13443,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13447,10 +13457,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13473,7 +13483,7 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>162</v>
@@ -13482,7 +13492,7 @@
         <v>162</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13532,7 +13542,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13553,10 +13563,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13567,10 +13577,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13593,19 +13603,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13654,7 +13664,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13675,10 +13685,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13689,10 +13699,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13715,13 +13725,13 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13772,7 +13782,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13796,7 +13806,7 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13807,10 +13817,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13839,7 +13849,7 @@
         <v>141</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>143</v>
@@ -13892,7 +13902,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13916,7 +13926,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13927,14 +13937,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13956,10 +13966,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14014,7 +14024,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14049,10 +14059,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14078,16 +14088,16 @@
         <v>188</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14112,13 +14122,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14136,7 +14146,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>94</v>
@@ -14154,16 +14164,16 @@
         <v>83</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
@@ -14171,10 +14181,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14197,13 +14207,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14254,7 +14264,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14278,7 +14288,7 @@
         <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14289,10 +14299,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14321,7 +14331,7 @@
         <v>141</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>143</v>
@@ -14362,19 +14372,19 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14398,7 +14408,7 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14409,10 +14419,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14420,7 +14430,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>82</v>
@@ -14435,19 +14445,19 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14484,17 +14494,17 @@
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14515,10 +14525,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14529,13 +14539,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>83</v>
@@ -14557,19 +14567,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14598,7 +14608,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -14616,7 +14626,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14637,10 +14647,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14651,10 +14661,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14677,13 +14687,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14734,7 +14744,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14758,7 +14768,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14769,10 +14779,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14801,7 +14811,7 @@
         <v>141</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>143</v>
@@ -14842,19 +14852,19 @@
         <v>83</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14878,7 +14888,7 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14889,10 +14899,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14918,23 +14928,23 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>83</v>
@@ -14976,7 +14986,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -14997,10 +15007,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15011,10 +15021,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15037,16 +15047,16 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15096,7 +15106,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15117,10 +15127,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15131,10 +15141,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15160,14 +15170,14 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15216,7 +15226,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15237,10 +15247,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15251,10 +15261,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15277,17 +15287,17 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15336,7 +15346,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15357,10 +15367,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15371,10 +15381,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15397,19 +15407,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15458,7 +15468,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15479,10 +15489,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15493,13 +15503,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15521,19 +15531,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15562,7 +15572,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15580,7 +15590,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15601,10 +15611,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15615,10 +15625,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15641,13 +15651,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15698,7 +15708,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15722,7 +15732,7 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15733,10 +15743,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15765,7 +15775,7 @@
         <v>141</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15806,19 +15816,19 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15842,7 +15852,7 @@
         <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15853,10 +15863,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15882,23 +15892,23 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -15940,7 +15950,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15961,10 +15971,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -15975,10 +15985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16001,16 +16011,16 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16060,7 +16070,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16081,10 +16091,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16095,10 +16105,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16124,14 +16134,14 @@
         <v>114</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16180,7 +16190,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16201,10 +16211,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16215,10 +16225,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16241,17 +16251,17 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16300,7 +16310,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16321,10 +16331,10 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16335,10 +16345,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16361,19 +16371,19 @@
         <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16422,7 +16432,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16443,10 +16453,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16457,10 +16467,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16483,19 +16493,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
@@ -16544,7 +16554,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16565,10 +16575,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16579,10 +16589,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16605,19 +16615,19 @@
         <v>95</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
@@ -16666,7 +16676,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16684,27 +16694,27 @@
         <v>83</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16730,16 +16740,16 @@
         <v>188</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -16764,13 +16774,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -16788,7 +16798,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -16797,7 +16807,7 @@
         <v>94</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>106</v>
@@ -16812,7 +16822,7 @@
         <v>137</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -16823,14 +16833,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16852,16 +16862,16 @@
         <v>188</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -16886,13 +16896,13 @@
         <v>83</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -16910,7 +16920,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16928,27 +16938,27 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16974,16 +16984,16 @@
         <v>84</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17032,7 +17042,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17053,10 +17063,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
